--- a/data/trending_integrated_20261030_15.xlsx
+++ b/data/trending_integrated_20261030_15.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32650</v>
+        <v>33050</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+262.78%</t>
+          <t>'+267.22%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="G2" t="n">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -601,7 +601,7 @@
         <v>19290</v>
       </c>
       <c r="L2" t="n">
-        <v>33800</v>
+        <v>35350</v>
       </c>
       <c r="M2" t="n">
         <v>16450</v>
@@ -610,10 +610,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1069784303115</v>
+        <v>1141978461840</v>
       </c>
       <c r="P2" t="n">
-        <v>33800</v>
+        <v>35350</v>
       </c>
       <c r="Q2" t="n">
         <v>16450</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정부 지원 AI 기업으로 IPO 기대감. 급등하는 주가와 함께 단기 투자 주의 의견.</t>
+          <t>강한 상승세 및 정부 정책 지원 기대감. 26년 IPO 대장 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '단타']</t>
+          <t>['AI', 'IPO', '정부 지원']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19290</v>
+        <v>19380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.86%</t>
+          <t>'+16.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -702,7 +702,7 @@
         <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>141746319180</v>
+        <v>143262317870</v>
       </c>
       <c r="P3" t="n">
         <v>22450</v>
@@ -718,12 +718,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 양자 보안 의무화 정책 수혜주로 주목받으며, 해킹 사태로 인한 반사이익 기대. 기술력과 향후 전망에 대한 긍정적 평가.</t>
+          <t>정부 양자 보안 의무화 수혜주로 주목. 전 세계 해킹 사태에 따른 최대 수혜 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.69%</t>
+          <t>'+14.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H4" t="n">
         <v>0.79</v>
@@ -794,7 +794,7 @@
         <v>0.63</v>
       </c>
       <c r="O4" t="n">
-        <v>13255659851</v>
+        <v>13363634430</v>
       </c>
       <c r="P4" t="n">
         <v>3170</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8720</v>
+        <v>8670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.25%</t>
+          <t>'+12.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>11224265370</v>
+        <v>11446078155</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7050</v>
+        <v>6710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.98%</t>
+          <t>'+7.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>41211234590</v>
+        <v>41839792280</v>
       </c>
       <c r="P6" t="n">
         <v>16620</v>
@@ -1023,79 +1023,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51500</v>
+        <v>29350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.89%</t>
+          <t>'+4.63%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.82</v>
+        <v>-0.36</v>
       </c>
       <c r="E7" t="n">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>262</v>
+        <v>399</v>
       </c>
       <c r="H7" t="n">
-        <v>23.82</v>
+        <v>4.69</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49100</v>
+        <v>28050</v>
       </c>
       <c r="K7" t="n">
-        <v>49450</v>
+        <v>27850</v>
       </c>
       <c r="L7" t="n">
-        <v>52000</v>
+        <v>30400</v>
       </c>
       <c r="M7" t="n">
-        <v>48050</v>
+        <v>27650</v>
       </c>
       <c r="N7" t="n">
-        <v>24.64</v>
+        <v>5.05</v>
       </c>
       <c r="O7" t="n">
-        <v>74222841150</v>
+        <v>134051418425</v>
       </c>
       <c r="P7" t="n">
-        <v>97900</v>
+        <v>50600</v>
       </c>
       <c r="Q7" t="n">
-        <v>30950</v>
+        <v>13210</v>
       </c>
       <c r="R7" t="n">
-        <v>5000</v>
+        <v>-40000</v>
       </c>
       <c r="S7" t="n">
-        <v>80000</v>
+        <v>228000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>TC본더 매출 본격화 및 사상 최대 실적 발표. 경쟁사 대비 저평가 분석 및 HBM 시대 수혜 기대.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', 'HBM']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,135 +1103,135 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15640</v>
+        <v>51200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.41%</t>
+          <t>'+4.28%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.9</v>
+        <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G8" t="n">
-        <v>445</v>
+        <v>265</v>
       </c>
       <c r="H8" t="n">
-        <v>7.15</v>
+        <v>23.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14980</v>
+        <v>49100</v>
       </c>
       <c r="K8" t="n">
-        <v>14980</v>
+        <v>49450</v>
       </c>
       <c r="L8" t="n">
-        <v>16150</v>
+        <v>52000</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>48050</v>
       </c>
       <c r="N8" t="n">
-        <v>8.050000000000001</v>
+        <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>58697319825</v>
+        <v>75987109900</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>97900</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>30950</v>
       </c>
       <c r="R8" t="n">
-        <v>84000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>179000</v>
+        <v>80000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>루닛의 FDA 승인 신청 및 미국 보험 등재 기대감. 유방암 위험 예측 솔루션의 시장 확대 전망. 공매도 압력에도 불구하고 주가 상승 가능성 언급.</t>
+          <t>TC본더 매출 본격화 및 사상 최대 실적 발표. 경쟁사 대비 저평가 분석 및 HBM 시대 수혜 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA 승인', '유방암', '공매도']</t>
+          <t>['실적', 'TC본더', 'HBM']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29200</v>
+        <v>15540</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.10%</t>
+          <t>'+3.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>399</v>
+        <v>458</v>
       </c>
       <c r="H9" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L9" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M9" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N9" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>132537280950</v>
+        <v>60218098645</v>
       </c>
       <c r="P9" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-40000</v>
+        <v>84000</v>
       </c>
       <c r="S9" t="n">
-        <v>228000</v>
+        <v>179000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
+          <t>루닛의 FDA 승인 신청 및 미국 보험 등재 기대감. 유방암 위험 예측 솔루션의 시장 확대 전망. 공매도 압력에도 불구하고 주가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇', '엑추에이터', '반도체']</t>
+          <t>['FDA 승인', '유방암', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11430</v>
+        <v>11380</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.05%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F10" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G10" t="n">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="H10" t="n">
         <v>15.04</v>
@@ -1346,7 +1346,7 @@
         <v>15.08</v>
       </c>
       <c r="O10" t="n">
-        <v>64093422625</v>
+        <v>64910475785</v>
       </c>
       <c r="P10" t="n">
         <v>18960</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15730</v>
+        <v>15840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.76%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>63132866525</v>
+        <v>65897657320</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 호조 및 해외 조선주 상승세와 대비되는 국내 주가 흐름. FLNG 2호기 수주 유력.</t>
+          <t>3분기 실적 호조 및 미국 조선주 강세와 대비되는 국내 조선주 약세. 델핀 FLNG 2호기 수주 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', 'FLNG', '수주']</t>
+          <t>['실적', '수주', '조선주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,18 +1487,18 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3965</v>
+        <v>4010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F12" t="n">
         <v>54</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>84997316016</v>
+        <v>85396935003</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7250</v>
+        <v>7260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H13" t="n">
         <v>25.3</v>
@@ -1622,7 +1622,7 @@
         <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>13795156085</v>
+        <v>14313702050</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60700</v>
+        <v>61050</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.34%</t>
+          <t>'-2.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F14" t="n">
         <v>47</v>
       </c>
       <c r="G14" t="n">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="H14" t="n">
         <v>41.76</v>
@@ -1714,7 +1714,7 @@
         <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>114434197950</v>
+        <v>117809980450</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1759,215 +1759,215 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6350</v>
+        <v>223750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.37%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>461</v>
       </c>
       <c r="G15" t="n">
-        <v>87</v>
+        <v>1127</v>
       </c>
       <c r="H15" t="n">
-        <v>0.85</v>
+        <v>46.17</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6640</v>
+        <v>232000</v>
       </c>
       <c r="K15" t="n">
-        <v>7210</v>
+        <v>223500</v>
       </c>
       <c r="L15" t="n">
-        <v>7500</v>
+        <v>229500</v>
       </c>
       <c r="M15" t="n">
-        <v>6230</v>
+        <v>216500</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9</v>
+        <v>46.19</v>
       </c>
       <c r="O15" t="n">
-        <v>32567378500</v>
+        <v>3539743875250</v>
       </c>
       <c r="P15" t="n">
-        <v>9820</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>4000</v>
+        <v>94500</v>
       </c>
       <c r="R15" t="n">
-        <v>-27000</v>
+        <v>538000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>이재용 경영 퇴출 및 자사주 매입/소각 촉구. 정치적 이슈와 주가 부진 연관성 주장.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['자사주', '경영', '주가 조작']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>221750</v>
+        <v>6370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.42%</t>
+          <t>'-4.07%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>76</v>
       </c>
       <c r="F16" t="n">
-        <v>480</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>1125</v>
+        <v>87</v>
       </c>
       <c r="H16" t="n">
-        <v>46.17</v>
+        <v>0.85</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>232000</v>
+        <v>6640</v>
       </c>
       <c r="K16" t="n">
-        <v>223500</v>
+        <v>7210</v>
       </c>
       <c r="L16" t="n">
-        <v>229500</v>
+        <v>7500</v>
       </c>
       <c r="M16" t="n">
-        <v>216500</v>
+        <v>6230</v>
       </c>
       <c r="N16" t="n">
-        <v>46.19</v>
+        <v>0.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3442219808250</v>
+        <v>32643597460</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>9820</v>
       </c>
       <c r="Q16" t="n">
-        <v>94500</v>
+        <v>4000</v>
       </c>
       <c r="R16" t="n">
-        <v>538000</v>
+        <v>-27000</v>
       </c>
       <c r="S16" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이재용 경영 퇴출 요구 및 자사주 매입/소각 촉구. 정치적 발언과 함께 주가 부양 의지 부족 비판.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '경영']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22350</v>
+        <v>54100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.30%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>276</v>
+        <v>398</v>
       </c>
       <c r="F17" t="n">
-        <v>178</v>
+        <v>250</v>
       </c>
       <c r="G17" t="n">
-        <v>667</v>
+        <v>1335</v>
       </c>
       <c r="H17" t="n">
-        <v>11.6</v>
+        <v>22.14</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>23600</v>
+        <v>56700</v>
       </c>
       <c r="K17" t="n">
-        <v>22650</v>
+        <v>55500</v>
       </c>
       <c r="L17" t="n">
-        <v>22750</v>
+        <v>55900</v>
       </c>
       <c r="M17" t="n">
-        <v>21100</v>
+        <v>53500</v>
       </c>
       <c r="N17" t="n">
-        <v>12.23</v>
+        <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>99079452650</v>
+        <v>111556273100</v>
       </c>
       <c r="P17" t="n">
-        <v>59300</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>21100</v>
+        <v>53400</v>
       </c>
       <c r="R17" t="n">
-        <v>-728000</v>
+        <v>-281000</v>
       </c>
       <c r="S17" t="n">
-        <v>-220000</v>
+        <v>-89000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>RE100 1조원 승인 및 미국 카터스빌 모듈 완판 소식에도 불구하고 주가 하락 및 유증에 대한 불만, 의도적 주가 누르기 의혹 제기.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 체코 원전 관련 손실 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['RE100', '카터스빌', '유증']</t>
+          <t>['SMR', '원자로 수주', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53600</v>
+        <v>22350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.47%</t>
+          <t>'-5.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.2</v>
+        <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="F18" t="n">
-        <v>247</v>
+        <v>179</v>
       </c>
       <c r="G18" t="n">
-        <v>1317</v>
+        <v>670</v>
       </c>
       <c r="H18" t="n">
-        <v>22.14</v>
+        <v>11.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>56700</v>
+        <v>23600</v>
       </c>
       <c r="K18" t="n">
-        <v>55500</v>
+        <v>22650</v>
       </c>
       <c r="L18" t="n">
-        <v>55900</v>
+        <v>22750</v>
       </c>
       <c r="M18" t="n">
-        <v>53500</v>
+        <v>21100</v>
       </c>
       <c r="N18" t="n">
-        <v>22.34</v>
+        <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>107042202000</v>
+        <v>100890183725</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>59300</v>
       </c>
       <c r="Q18" t="n">
-        <v>53400</v>
+        <v>21100</v>
       </c>
       <c r="R18" t="n">
-        <v>-281000</v>
+        <v>-728000</v>
       </c>
       <c r="S18" t="n">
-        <v>-89000</v>
+        <v>-220000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 정부 정책 및 국내 증시 상황과의 연관성 언급.</t>
+          <t>RE100 1조원 승인 및 미국 카터스빌 모듈 완판 소식에도 불구하고 주가 하락 및 유증에 대한 불만, 의도적 주가 누르기 의혹 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SMR', '원자로', '실적']</t>
+          <t>['RE100', '카터스빌', '유증']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8110</v>
+        <v>8100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-5.59%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>68</v>
       </c>
       <c r="G19" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H19" t="n">
         <v>2.67</v>
@@ -2174,7 +2174,7 @@
         <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>31097583735</v>
+        <v>31216003815</v>
       </c>
       <c r="P19" t="n">
         <v>19270</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>172600</v>
+        <v>173400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.14%</t>
+          <t>'-5.71%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G20" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>729971805700</v>
+        <v>746589285450</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2326,13 +2326,13 @@
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="F21" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G21" t="n">
-        <v>1516</v>
+        <v>1536</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2358,7 +2358,7 @@
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>67225803775</v>
+        <v>68740535220</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2403,83 +2403,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1394000</v>
+        <v>13870</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.65%</t>
+          <t>'-7.72%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="E22" t="n">
-        <v>800</v>
+        <v>133</v>
       </c>
       <c r="F22" t="n">
-        <v>437</v>
+        <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>1222</v>
+        <v>543</v>
       </c>
       <c r="H22" t="n">
-        <v>48.72</v>
+        <v>3.13</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1526000</v>
+        <v>15030</v>
       </c>
       <c r="K22" t="n">
-        <v>1444000</v>
+        <v>14500</v>
       </c>
       <c r="L22" t="n">
-        <v>1449000</v>
+        <v>14570</v>
       </c>
       <c r="M22" t="n">
-        <v>1381000</v>
+        <v>13590</v>
       </c>
       <c r="N22" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="O22" t="n">
-        <v>4157137058500</v>
+        <v>51883841065</v>
       </c>
       <c r="P22" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>501000</v>
+        <v>1830</v>
       </c>
       <c r="R22" t="n">
-        <v>-177000</v>
+        <v>-225000</v>
       </c>
       <c r="S22" t="n">
-        <v>-59000</v>
+        <v>-65000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>자사주 매입 및 AI 투자 확대 뉴스에 대한 기대감. 정치적 이슈와 함께 변동성 높은 주가 흐름.</t>
+          <t>27년까지의 성장 전망 및 광통신 섹터 호재에도 불구하고 국내 증시 불신으로 인한 주가 하락, 공매도 세력 비판.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주', 'AI', '투자']</t>
+          <t>['광통신', '특허', '호재']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13700</v>
+        <v>1404000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.85%</t>
+          <t>'-7.99%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E23" t="n">
-        <v>132</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>71</v>
+        <v>442</v>
       </c>
       <c r="G23" t="n">
-        <v>535</v>
+        <v>1192</v>
       </c>
       <c r="H23" t="n">
-        <v>3.13</v>
+        <v>48.72</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>15030</v>
+        <v>1526000</v>
       </c>
       <c r="K23" t="n">
-        <v>14500</v>
+        <v>1444000</v>
       </c>
       <c r="L23" t="n">
-        <v>14570</v>
+        <v>1449000</v>
       </c>
       <c r="M23" t="n">
-        <v>13590</v>
+        <v>1381000</v>
       </c>
       <c r="N23" t="n">
-        <v>3.33</v>
+        <v>48.66</v>
       </c>
       <c r="O23" t="n">
-        <v>51197545185</v>
+        <v>4294662002000</v>
       </c>
       <c r="P23" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>1830</v>
+        <v>501000</v>
       </c>
       <c r="R23" t="n">
-        <v>-225000</v>
+        <v>-177000</v>
       </c>
       <c r="S23" t="n">
-        <v>-65000</v>
+        <v>-59000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>27년까지의 성장 전망 및 광통신 섹터 호재에도 불구하고 국내 증시 불신으로 인한 주가 하락, 공매도 세력 비판.</t>
+          <t>장중 프로그램 순매수 유입 및 샌디스크 서프라이즈 소식에 대한 기대감. 자사주 매입 호재 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '호재']</t>
+          <t>['자사주 매입', '순매수', '서프라이즈']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -2602,13 +2602,13 @@
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F24" t="n">
         <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2628,13 +2628,13 @@
         <v>8130</v>
       </c>
       <c r="M24" t="n">
-        <v>6940</v>
+        <v>6920</v>
       </c>
       <c r="N24" t="n">
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>18080098470</v>
+        <v>18410593650</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117800</v>
+        <v>117900</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-14.76%</t>
+          <t>'-14.69%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2697,10 +2697,10 @@
         <v>209</v>
       </c>
       <c r="F25" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G25" t="n">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="H25" t="n">
         <v>14.2</v>
@@ -2726,7 +2726,7 @@
         <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>203915084500</v>
+        <v>208005001250</v>
       </c>
       <c r="P25" t="n">
         <v>198000</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13360</v>
+        <v>13600</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-21.41%</t>
+          <t>'-20.00%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.01</v>
       </c>
       <c r="E26" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F26" t="n">
         <v>106</v>
       </c>
       <c r="G26" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H26" t="n">
         <v>0.66</v>
@@ -2818,7 +2818,7 @@
         <v>0.65</v>
       </c>
       <c r="O26" t="n">
-        <v>71203808190</v>
+        <v>71867530545</v>
       </c>
       <c r="P26" t="n">
         <v>28800</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회와 반도체 섹터 약세에 따른 주가 급락. 개미 투자자들의 어려움 토로.</t>
+          <t>보호예수 물량 출회 속 거래대금 부진. 반도체 업종 약세 영향 및 개인 수익 부재 지적.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '급락']</t>
+          <t>['보호예수', '거래대금', '반도체']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>1.45</v>
       </c>
       <c r="E27" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F27" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G27" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H27" t="n">
         <v>4.8</v>
@@ -2910,7 +2910,7 @@
         <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>8493043723</v>
+        <v>8500377438</v>
       </c>
       <c r="P27" t="n">
         <v>5700</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9730</v>
+        <v>9600</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-35.13%</t>
+          <t>'-36.00%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="F28" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G28" t="n">
-        <v>1001</v>
+        <v>1034</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>150737510215</v>
+        <v>153776022785</v>
       </c>
       <c r="P28" t="n">
         <v>12700</v>

--- a/data/trending_integrated_20261030_15.xlsx
+++ b/data/trending_integrated_20261030_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33050</v>
+        <v>30250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+267.22%</t>
+          <t>'+236.11%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G2" t="n">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1141978461840</v>
+        <v>1183844686740</v>
       </c>
       <c r="P2" t="n">
         <v>35350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>강한 상승세 및 정부 정책 지원 기대감. 26년 IPO 대장 가능성 언급.</t>
+          <t>급격한 주가 상승에 대한 기대감이 매우 높으며, 정부의 AI 육성 정책과 연관 지어 긍정적으로 해석하려는 경향이 강함. IPO 관련 언급도 있으나 구체적인 팩트 기반은 부족.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '정부 지원']</t>
+          <t>['AI', 'IPO', '급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,184 +655,184 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19380</v>
+        <v>3000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.40%</t>
+          <t>'+22.45%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.75</v>
+        <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>241</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>0.79</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16650</v>
+        <v>2450</v>
       </c>
       <c r="K3" t="n">
-        <v>16830</v>
+        <v>2460</v>
       </c>
       <c r="L3" t="n">
-        <v>19900</v>
+        <v>3110</v>
       </c>
       <c r="M3" t="n">
-        <v>16750</v>
+        <v>2335</v>
       </c>
       <c r="N3" t="n">
-        <v>4.35</v>
+        <v>0.63</v>
       </c>
       <c r="O3" t="n">
-        <v>143262317870</v>
+        <v>13786409271</v>
       </c>
       <c r="P3" t="n">
-        <v>22450</v>
+        <v>3170</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>880</v>
       </c>
       <c r="R3" t="n">
-        <v>69000</v>
+        <v>-24000</v>
       </c>
       <c r="S3" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 양자 보안 의무화 수혜주로 주목. 전 세계 해킹 사태에 따른 최대 수혜 기대감.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자 보안', '수혜주', '해킹']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>진양화학</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2805</v>
+        <v>19410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.49%</t>
+          <t>'+16.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.16</v>
+        <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>240</v>
       </c>
       <c r="H4" t="n">
-        <v>0.79</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2450</v>
+        <v>16650</v>
       </c>
       <c r="K4" t="n">
-        <v>2460</v>
+        <v>16830</v>
       </c>
       <c r="L4" t="n">
-        <v>3110</v>
+        <v>19900</v>
       </c>
       <c r="M4" t="n">
-        <v>2335</v>
+        <v>16750</v>
       </c>
       <c r="N4" t="n">
-        <v>0.63</v>
+        <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>13363634430</v>
+        <v>144641732010</v>
       </c>
       <c r="P4" t="n">
-        <v>3170</v>
+        <v>22450</v>
       </c>
       <c r="Q4" t="n">
-        <v>880</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-24000</v>
+        <v>69000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
+          <t>정부 양자 보안 의무화 수혜주로 주목. 전 세계 해킹 사태에 따른 최대 수혜 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
+          <t>['양자 보안', '수혜주', '해킹']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>051630</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8670</v>
+        <v>8720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.60%</t>
+          <t>'+13.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
         <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H5" t="n">
         <v>13.29</v>
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>11446078155</v>
+        <v>11552974785</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6710</v>
+        <v>6720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.53%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>41839792280</v>
+        <v>42623847930</v>
       </c>
       <c r="P6" t="n">
         <v>16620</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>건설업 부활에 대한 기대감과 함께 급등 및 연상에 대한 언급. 유증 성공 여부 및 주가 움직임에 대한 관심 표출.</t>
+          <t>주가 급등 및 연상에 대한 기대감이 있으나, 유증 및 주포의 행태에 대한 부정적 언급도 혼재되어 있어 팩트 기반은 약함. 건설 산업 전반의 중요성을 강조하는 의견도 포함됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설업', '급등', '유증']</t>
+          <t>['급등', '유증', '주포']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29350</v>
+        <v>29450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.63%</t>
+          <t>'+4.99%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.36</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>4.69</v>
@@ -1070,7 +1070,7 @@
         <v>5.05</v>
       </c>
       <c r="O7" t="n">
-        <v>134051418425</v>
+        <v>136080152250</v>
       </c>
       <c r="P7" t="n">
         <v>50600</v>
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51200</v>
+        <v>15690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.28%</t>
+          <t>'+4.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.82</v>
+        <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
-        <v>265</v>
+        <v>470</v>
       </c>
       <c r="H8" t="n">
-        <v>23.82</v>
+        <v>7.15</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49100</v>
+        <v>14980</v>
       </c>
       <c r="K8" t="n">
-        <v>49450</v>
+        <v>14980</v>
       </c>
       <c r="L8" t="n">
-        <v>52000</v>
+        <v>16150</v>
       </c>
       <c r="M8" t="n">
-        <v>48050</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>24.64</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>75987109900</v>
+        <v>60754673975</v>
       </c>
       <c r="P8" t="n">
-        <v>97900</v>
+        <v>49800</v>
       </c>
       <c r="Q8" t="n">
-        <v>30950</v>
+        <v>8180</v>
       </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>84000</v>
       </c>
       <c r="S8" t="n">
-        <v>80000</v>
+        <v>179000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>TC본더 매출 본격화 및 사상 최대 실적 발표. 경쟁사 대비 저평가 분석 및 HBM 시대 수혜 기대.</t>
+          <t>루닛의 FDA 승인 신청 및 미국 보험 등재 기대감. 유방암 위험 예측 솔루션의 시장 확대 전망. 공매도 압력에도 불구하고 주가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', 'HBM']</t>
+          <t>['FDA 승인', '유방암', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15540</v>
+        <v>51400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.74%</t>
+          <t>'+4.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
-        <v>458</v>
+        <v>267</v>
       </c>
       <c r="H9" t="n">
-        <v>7.15</v>
+        <v>23.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>49100</v>
       </c>
       <c r="K9" t="n">
-        <v>14980</v>
+        <v>49450</v>
       </c>
       <c r="L9" t="n">
-        <v>16150</v>
+        <v>52000</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>48050</v>
       </c>
       <c r="N9" t="n">
-        <v>8.050000000000001</v>
+        <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>60218098645</v>
+        <v>76892122300</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>97900</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>30950</v>
       </c>
       <c r="R9" t="n">
-        <v>84000</v>
+        <v>5000</v>
       </c>
       <c r="S9" t="n">
-        <v>179000</v>
+        <v>80000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>루닛의 FDA 승인 신청 및 미국 보험 등재 기대감. 유방암 위험 예측 솔루션의 시장 확대 전망. 공매도 압력에도 불구하고 주가 상승 가능성 언급.</t>
+          <t>TC본더 매출 본격화 및 사상 최대 실적 발표. 경쟁사 대비 저평가 분석 및 HBM 시대 수혜 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA 승인', '유방암', '공매도']</t>
+          <t>['실적', 'TC본더', 'HBM']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11380</v>
+        <v>11670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+4.20%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F10" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G10" t="n">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="H10" t="n">
         <v>15.04</v>
@@ -1346,7 +1346,7 @@
         <v>15.08</v>
       </c>
       <c r="O10" t="n">
-        <v>64910475785</v>
+        <v>65775375835</v>
       </c>
       <c r="P10" t="n">
         <v>18960</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15840</v>
+        <v>15810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.76%</t>
+          <t>'+0.57%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F11" t="n">
         <v>75</v>
       </c>
       <c r="G11" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>65897657320</v>
+        <v>70178454790</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4010</v>
+        <v>3985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'-1.36%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>54</v>
       </c>
       <c r="G12" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>85396935003</v>
+        <v>85837351162</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7260</v>
+        <v>61400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-2.23%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>264</v>
+        <v>453</v>
       </c>
       <c r="H13" t="n">
-        <v>25.3</v>
+        <v>41.76</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7450</v>
+        <v>62800</v>
       </c>
       <c r="K13" t="n">
-        <v>7350</v>
+        <v>62300</v>
       </c>
       <c r="L13" t="n">
-        <v>7570</v>
+        <v>62800</v>
       </c>
       <c r="M13" t="n">
-        <v>7220</v>
+        <v>60400</v>
       </c>
       <c r="N13" t="n">
-        <v>25.32</v>
+        <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>14313702050</v>
+        <v>124127432900</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>7010</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>-46000</v>
+        <v>-65000</v>
       </c>
       <c r="S13" t="n">
-        <v>-8000</v>
+        <v>-81000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61050</v>
+        <v>7280</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.79%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>445</v>
+        <v>279</v>
       </c>
       <c r="H14" t="n">
-        <v>41.76</v>
+        <v>25.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62800</v>
+        <v>7450</v>
       </c>
       <c r="K14" t="n">
-        <v>62300</v>
+        <v>7350</v>
       </c>
       <c r="L14" t="n">
-        <v>62800</v>
+        <v>7570</v>
       </c>
       <c r="M14" t="n">
-        <v>60400</v>
+        <v>7220</v>
       </c>
       <c r="N14" t="n">
-        <v>41.55</v>
+        <v>25.32</v>
       </c>
       <c r="O14" t="n">
-        <v>117809980450</v>
+        <v>14880229690</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>7010</v>
       </c>
       <c r="R14" t="n">
-        <v>-65000</v>
+        <v>-46000</v>
       </c>
       <c r="S14" t="n">
-        <v>-81000</v>
+        <v>-8000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>223750</v>
+        <v>225000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1777,10 +1777,10 @@
         <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="G15" t="n">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="H15" t="n">
         <v>46.17</v>
@@ -1806,7 +1806,7 @@
         <v>46.19</v>
       </c>
       <c r="O15" t="n">
-        <v>3539743875250</v>
+        <v>3686026755250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>이재용 경영 퇴출 및 자사주 매입/소각 촉구. 정치적 이슈와 주가 부진 연관성 주장.</t>
+          <t>정치적 이슈와 관련된 부정적 언급이 다수 관찰되며, 주가 하락에 대한 정치적 책임론이 제기됨.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주', '경영', '주가 조작']</t>
+          <t>['정치', '주가 하락', '책임론']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6370</v>
+        <v>6410</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.07%</t>
+          <t>'-3.46%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H16" t="n">
         <v>0.85</v>
@@ -1898,7 +1898,7 @@
         <v>0.9</v>
       </c>
       <c r="O16" t="n">
-        <v>32643597460</v>
+        <v>32736615240</v>
       </c>
       <c r="P16" t="n">
         <v>9820</v>
@@ -1943,123 +1943,123 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54100</v>
+        <v>8270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.2</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>398</v>
+        <v>119</v>
       </c>
       <c r="F17" t="n">
-        <v>250</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
-        <v>1335</v>
+        <v>322</v>
       </c>
       <c r="H17" t="n">
-        <v>22.14</v>
+        <v>2.67</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>56700</v>
+        <v>8580</v>
       </c>
       <c r="K17" t="n">
-        <v>55500</v>
+        <v>11090</v>
       </c>
       <c r="L17" t="n">
-        <v>55900</v>
+        <v>11150</v>
       </c>
       <c r="M17" t="n">
-        <v>53500</v>
+        <v>8000</v>
       </c>
       <c r="N17" t="n">
-        <v>22.34</v>
+        <v>2.66</v>
       </c>
       <c r="O17" t="n">
-        <v>111556273100</v>
+        <v>31337216265</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>19270</v>
       </c>
       <c r="Q17" t="n">
-        <v>53400</v>
+        <v>2135</v>
       </c>
       <c r="R17" t="n">
-        <v>-281000</v>
+        <v>-396000</v>
       </c>
       <c r="S17" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 소식. 체코 원전 관련 손실 및 정부 정책 비판.</t>
+          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '원자로 수주', '실적']</t>
+          <t>['광반도체', '와이캅3', '환기']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22350</v>
+        <v>54500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.30%</t>
+          <t>'-3.88%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
       <c r="E18" t="n">
-        <v>279</v>
+        <v>403</v>
       </c>
       <c r="F18" t="n">
-        <v>179</v>
+        <v>251</v>
       </c>
       <c r="G18" t="n">
-        <v>670</v>
+        <v>1387</v>
       </c>
       <c r="H18" t="n">
-        <v>11.6</v>
+        <v>22.14</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>23600</v>
+        <v>56700</v>
       </c>
       <c r="K18" t="n">
-        <v>22650</v>
+        <v>55500</v>
       </c>
       <c r="L18" t="n">
-        <v>22750</v>
+        <v>55900</v>
       </c>
       <c r="M18" t="n">
-        <v>21100</v>
+        <v>53500</v>
       </c>
       <c r="N18" t="n">
-        <v>12.23</v>
+        <v>22.34</v>
       </c>
       <c r="O18" t="n">
-        <v>100890183725</v>
+        <v>119983956150</v>
       </c>
       <c r="P18" t="n">
-        <v>59300</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>21100</v>
+        <v>53400</v>
       </c>
       <c r="R18" t="n">
-        <v>-728000</v>
+        <v>-281000</v>
       </c>
       <c r="S18" t="n">
-        <v>-220000</v>
+        <v>-89000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>RE100 1조원 승인 및 미국 카터스빌 모듈 완판 소식에도 불구하고 주가 하락 및 유증에 대한 불만, 의도적 주가 누르기 의혹 제기.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 관련 긍정적 뉴스가 있으나, 체코 원전 사업 관련 부정적 언급과 함께 정부 정책에 대한 불만 표현이 혼재됨.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['RE100', '카터스빌', '유증']</t>
+          <t>['SMR', '원전 수주', '실적']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,99 +2120,99 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8100</v>
+        <v>22550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.59%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.01</v>
+        <v>-0.63</v>
       </c>
       <c r="E19" t="n">
-        <v>118</v>
+        <v>283</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="G19" t="n">
-        <v>320</v>
+        <v>672</v>
       </c>
       <c r="H19" t="n">
-        <v>2.67</v>
+        <v>11.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8580</v>
+        <v>23600</v>
       </c>
       <c r="K19" t="n">
-        <v>11090</v>
+        <v>22650</v>
       </c>
       <c r="L19" t="n">
-        <v>11150</v>
+        <v>22750</v>
       </c>
       <c r="M19" t="n">
-        <v>8000</v>
+        <v>21100</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>12.23</v>
       </c>
       <c r="O19" t="n">
-        <v>31216003815</v>
+        <v>102463678475</v>
       </c>
       <c r="P19" t="n">
-        <v>19270</v>
+        <v>59300</v>
       </c>
       <c r="Q19" t="n">
-        <v>2135</v>
+        <v>21100</v>
       </c>
       <c r="R19" t="n">
-        <v>-396000</v>
+        <v>-728000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-220000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
+          <t>RE100 1조원 승인 및 미국 카터스빌 모듈 완판 소식에도 불구하고 주가 하락 및 유증에 대한 불만, 의도적 주가 누르기 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광반도체', '와이캅3', '환기']</t>
+          <t>['RE100', '카터스빌', '유증']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>173400</v>
+        <v>174000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.71%</t>
+          <t>'-5.38%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>746589285450</v>
+        <v>766178676600</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10840</v>
+        <v>10900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.71%</t>
+          <t>'-6.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="F21" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G21" t="n">
-        <v>1536</v>
+        <v>1560</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2358,7 +2358,7 @@
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>68740535220</v>
+        <v>70062112580</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>원전, 가덕도 공사비 증액 및 공매도 금지 조치에 따른 기대감. 한수원 갑질 논란 속 재건 사업 전망.</t>
+          <t>원전 사업 증액, 가덕도 신공항 이슈와 연계된 긍정적 기대감과 함께 공매도 금지 조치에 대한 언급이 있음. 일부 내용은 사실 기반이나 과장된 기대가 포함됨.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['원전', '공사비', '공매도']</t>
+          <t>['원전', '가덕도', '공매도 금지']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,83 +2403,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13870</v>
+        <v>1411000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.72%</t>
+          <t>'-7.54%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E22" t="n">
-        <v>133</v>
+        <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>71</v>
+        <v>443</v>
       </c>
       <c r="G22" t="n">
-        <v>543</v>
+        <v>1189</v>
       </c>
       <c r="H22" t="n">
-        <v>3.13</v>
+        <v>48.72</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>15030</v>
+        <v>1526000</v>
       </c>
       <c r="K22" t="n">
-        <v>14500</v>
+        <v>1444000</v>
       </c>
       <c r="L22" t="n">
-        <v>14570</v>
+        <v>1449000</v>
       </c>
       <c r="M22" t="n">
-        <v>13590</v>
+        <v>1381000</v>
       </c>
       <c r="N22" t="n">
-        <v>3.33</v>
+        <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>51883841065</v>
+        <v>4413193597000</v>
       </c>
       <c r="P22" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q22" t="n">
-        <v>1830</v>
+        <v>501000</v>
       </c>
       <c r="R22" t="n">
-        <v>-225000</v>
+        <v>-177000</v>
       </c>
       <c r="S22" t="n">
-        <v>-65000</v>
+        <v>-59000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>27년까지의 성장 전망 및 광통신 섹터 호재에도 불구하고 국내 증시 불신으로 인한 주가 하락, 공매도 세력 비판.</t>
+          <t>정치적 이슈와 함께 주가 반등에 대한 기대감이 일부 존재하나, 감정적 표현과 불확실한 전망이 주를 이룸. 자사주 매입 관련 언급이 있으나 구체적인 근거 부족.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '호재']</t>
+          <t>['자사주 매입', '주가 반등', 'AI']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,77 +2488,77 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1404000</v>
+        <v>13800</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-7.99%</t>
+          <t>'-8.18%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.06</v>
+        <v>-0.2</v>
       </c>
       <c r="E23" t="n">
-        <v>800</v>
+        <v>135</v>
       </c>
       <c r="F23" t="n">
-        <v>442</v>
+        <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>1192</v>
+        <v>552</v>
       </c>
       <c r="H23" t="n">
-        <v>48.72</v>
+        <v>3.13</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1526000</v>
+        <v>15030</v>
       </c>
       <c r="K23" t="n">
-        <v>1444000</v>
+        <v>14500</v>
       </c>
       <c r="L23" t="n">
-        <v>1449000</v>
+        <v>14570</v>
       </c>
       <c r="M23" t="n">
-        <v>1381000</v>
+        <v>13590</v>
       </c>
       <c r="N23" t="n">
-        <v>48.66</v>
+        <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>4294662002000</v>
+        <v>52974447170</v>
       </c>
       <c r="P23" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q23" t="n">
-        <v>501000</v>
+        <v>1830</v>
       </c>
       <c r="R23" t="n">
-        <v>-177000</v>
+        <v>-225000</v>
       </c>
       <c r="S23" t="n">
-        <v>-59000</v>
+        <v>-65000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>장중 프로그램 순매수 유입 및 샌디스크 서프라이즈 소식에 대한 기대감. 자사주 매입 호재 언급.</t>
+          <t>27년까지의 성장 전망 및 광통신 섹터 호재에도 불구하고 국내 증시 불신으로 인한 주가 하락, 공매도 세력 비판.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['자사주 매입', '순매수', '서프라이즈']</t>
+          <t>['광통신', '특허', '호재']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6980</v>
+        <v>7010</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-11.65%</t>
+          <t>'-11.27%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F24" t="n">
         <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>18410593650</v>
+        <v>18569393555</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2679,31 +2679,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117900</v>
+        <v>95800</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-14.69%</t>
+          <t>'-11.54%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="E25" t="n">
-        <v>209</v>
+        <v>383</v>
       </c>
       <c r="F25" t="n">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="G25" t="n">
-        <v>631</v>
+        <v>1574</v>
       </c>
       <c r="H25" t="n">
-        <v>14.2</v>
+        <v>39.05</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2711,47 +2711,47 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>138200</v>
+        <v>108300</v>
       </c>
       <c r="K25" t="n">
-        <v>132600</v>
+        <v>106400</v>
       </c>
       <c r="L25" t="n">
-        <v>132900</v>
+        <v>106400</v>
       </c>
       <c r="M25" t="n">
-        <v>114300</v>
+        <v>93400</v>
       </c>
       <c r="N25" t="n">
-        <v>14.46</v>
+        <v>39.08</v>
       </c>
       <c r="O25" t="n">
-        <v>208005001250</v>
+        <v>183141990500</v>
       </c>
       <c r="P25" t="n">
-        <v>198000</v>
+        <v>212500</v>
       </c>
       <c r="Q25" t="n">
-        <v>36450</v>
+        <v>93400</v>
       </c>
       <c r="R25" t="n">
-        <v>-362000</v>
+        <v>-99000</v>
       </c>
       <c r="S25" t="n">
-        <v>-79000</v>
+        <v>7000</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>실적 발표 지연 및 주가 급락. SK하이닉스 물량 확대 관련 뉴스 언급 및 목표가 상향 분석.</t>
+          <t>큰 폭의 주가 하락에 대한 불만이 표출되며, 회사 실적 및 주가 조작 의혹에 대한 부정적 인식이 강하게 나타남. 컨센서스 대비 호실적 언급도 있으나 하락세를 상쇄하지 못함.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['실적', 'SK하이닉스', '목표가']</t>
+          <t>['주가 하락', '실적', '주가 조작']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2764,90 +2764,90 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>000270</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13600</v>
+        <v>119400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-20.00%</t>
+          <t>'-13.60%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="E26" t="n">
-        <v>309</v>
+        <v>220</v>
       </c>
       <c r="F26" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="G26" t="n">
-        <v>289</v>
+        <v>653</v>
       </c>
       <c r="H26" t="n">
-        <v>0.66</v>
+        <v>14.2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>17000</v>
+        <v>138200</v>
       </c>
       <c r="K26" t="n">
-        <v>14000</v>
+        <v>132600</v>
       </c>
       <c r="L26" t="n">
-        <v>15280</v>
+        <v>132900</v>
       </c>
       <c r="M26" t="n">
-        <v>12930</v>
+        <v>114300</v>
       </c>
       <c r="N26" t="n">
-        <v>0.65</v>
+        <v>14.46</v>
       </c>
       <c r="O26" t="n">
-        <v>71867530545</v>
+        <v>213193433750</v>
       </c>
       <c r="P26" t="n">
-        <v>28800</v>
+        <v>198000</v>
       </c>
       <c r="Q26" t="n">
-        <v>11550</v>
+        <v>36450</v>
       </c>
       <c r="R26" t="n">
-        <v>-16000</v>
+        <v>-362000</v>
       </c>
       <c r="S26" t="n">
-        <v>-193000</v>
+        <v>-79000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 속 거래대금 부진. 반도체 업종 약세 영향 및 개인 수익 부재 지적.</t>
+          <t>실적 발표 지연 및 주가 급락. SK하이닉스 물량 확대 관련 뉴스 언급 및 목표가 상향 분석.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['보호예수', '거래대금', '반도체']</t>
+          <t>['실적', 'SK하이닉스', '목표가']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>353200</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>벡트로보틱스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1805</v>
+        <v>13680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-29.90%</t>
+          <t>'-19.53%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.45</v>
+        <v>0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>132</v>
+        <v>314</v>
       </c>
       <c r="F27" t="n">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="G27" t="n">
-        <v>127</v>
+        <v>291</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>0.66</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,51 +2895,51 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2575</v>
+        <v>17000</v>
       </c>
       <c r="K27" t="n">
-        <v>1960</v>
+        <v>14000</v>
       </c>
       <c r="L27" t="n">
-        <v>2005</v>
+        <v>15280</v>
       </c>
       <c r="M27" t="n">
-        <v>1805</v>
+        <v>12930</v>
       </c>
       <c r="N27" t="n">
-        <v>3.35</v>
+        <v>0.65</v>
       </c>
       <c r="O27" t="n">
-        <v>8500377438</v>
+        <v>72871334870</v>
       </c>
       <c r="P27" t="n">
-        <v>5700</v>
+        <v>28800</v>
       </c>
       <c r="Q27" t="n">
-        <v>1401</v>
+        <v>11550</v>
       </c>
       <c r="R27" t="n">
-        <v>-43000</v>
+        <v>-16000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-193000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>하한가 기록, 상폐 우려 및 자금 납입 지연 가능성 언급, 공시 및 납입 여부에 따른 주가 변동성 예상.</t>
+          <t>보호예수 물량 출회와 반도체 시장 약세 속에서 주가 하락에 대한 불만이 제기됨. 일부는 매수 기회로 보지만, 전체적으로 부정적인 논조가 강함.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['하한가', '상폐', '납입']</t>
+          <t>['보호예수', '반도체', '주가 하락']</t>
         </is>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2948,86 +2948,86 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>457600</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>벡트로보틱스</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9600</v>
+        <v>1805</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>'-36.00%</t>
+          <t>'-29.90%</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E28" t="n">
+        <v>137</v>
+      </c>
+      <c r="F28" t="n">
+        <v>61</v>
+      </c>
+      <c r="G28" t="n">
+        <v>137</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1805</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8537172363</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-43000</v>
+      </c>
+      <c r="S28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>629</v>
-      </c>
-      <c r="F28" t="n">
-        <v>252</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1034</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M28" t="n">
-        <v>9400</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>153776022785</v>
-      </c>
-      <c r="P28" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>9400</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-41000</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-265000</v>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>상장 후 주가 급락 및 상장 주관사 사기 의혹 제기. 높은 영업이익 대비 주가 부진. 인텔리빅스와의 비교 및 크리에이츠의 알짜배기 속성 강조. 실내 골프 대중화 전망.</t>
+          <t>하한가 기록 및 부도, 상폐 우려가 제기되며 매우 부정적인 심리가 지배적임. 납입 여부 및 공시 내용에 대한 불확실성이 높으며, 주가 조작 가능성에 대한 의혹도 제기됨.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부진', '실내 골프']</t>
+          <t>['하한가', '부도', '상폐']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3039,6 +3039,98 @@
         </is>
       </c>
       <c r="Z28" t="inlineStr">
+        <is>
+          <t>457600</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9410</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>'-37.27%</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>637</v>
+      </c>
+      <c r="F29" t="n">
+        <v>253</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1037</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K29" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9380</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>155476940960</v>
+      </c>
+      <c r="P29" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>9380</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-41000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-265000</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>높은 영업이익과 매출액을 근거로 긍정적 전망이 제시되며, 경쟁사(인텔리빅스) 대비 우수한 재무 상태를 강조함. 상장 초기의 변동성에 대한 언급도 있음.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>['영업이익', '매출', '알짜배기']</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>439270</t>
         </is>

--- a/data/trending_integrated_20261030_15.xlsx
+++ b/data/trending_integrated_20261030_15.xlsx
@@ -567,11 +567,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30250</v>
+        <v>31000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+236.11%</t>
+          <t>'+244.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -581,7 +581,7 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="G2" t="n">
         <v>782</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1183844686740</v>
+        <v>1189537526740</v>
       </c>
       <c r="P2" t="n">
         <v>35350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급격한 주가 상승에 대한 기대감이 매우 높으며, 정부의 AI 육성 정책과 연관 지어 긍정적으로 해석하려는 경향이 강함. IPO 관련 언급도 있으나 구체적인 팩트 기반은 부족.</t>
+          <t>AI 관련주로 분류되며 강한 상승 기대감 표출. IPO 관련 내용 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '급등']</t>
+          <t>['AI', 'IPO', '상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
         <v>0.79</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19410</v>
+        <v>19450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.58%</t>
+          <t>'+16.82%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>144641732010</v>
+        <v>145543239510</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8720</v>
+        <v>8680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.25%</t>
+          <t>'+12.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H5" t="n">
         <v>13.29</v>
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>11552974785</v>
+        <v>11654105465</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6720</v>
+        <v>6790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.69%</t>
+          <t>'+8.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F6" t="n">
         <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>42623847930</v>
+        <v>42732270650</v>
       </c>
       <c r="P6" t="n">
         <v>16620</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 급등 및 연상에 대한 기대감이 있으나, 유증 및 주포의 행태에 대한 부정적 언급도 혼재되어 있어 팩트 기반은 약함. 건설 산업 전반의 중요성을 강조하는 의견도 포함됨.</t>
+          <t>급등 및 하락에 대한 혼조된 의견. 건설주로서의 역할에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['급등', '유증', '주포']</t>
+          <t>['급등', '건설', '주가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29450</v>
+        <v>29500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.99%</t>
+          <t>'+5.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1070,7 +1070,7 @@
         <v>5.05</v>
       </c>
       <c r="O7" t="n">
-        <v>136080152250</v>
+        <v>137567866750</v>
       </c>
       <c r="P7" t="n">
         <v>50600</v>
@@ -1130,13 +1130,13 @@
         <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H8" t="n">
         <v>7.15</v>
@@ -1162,7 +1162,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>60754673975</v>
+        <v>61422048125</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51400</v>
+        <v>51300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.68%</t>
+          <t>'+4.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="H9" t="n">
         <v>23.82</v>
@@ -1254,7 +1254,7 @@
         <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>76892122300</v>
+        <v>77582928100</v>
       </c>
       <c r="P9" t="n">
         <v>97900</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11670</v>
+        <v>11640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.20%</t>
+          <t>'+3.93%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F10" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G10" t="n">
-        <v>1056</v>
+        <v>1080</v>
       </c>
       <c r="H10" t="n">
         <v>15.04</v>
@@ -1346,7 +1346,7 @@
         <v>15.08</v>
       </c>
       <c r="O10" t="n">
-        <v>65775375835</v>
+        <v>66303063595</v>
       </c>
       <c r="P10" t="n">
         <v>18960</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>세계 1위 희토류 없는 백색 LED 개발 및 기술력 강조. 100억 달러 시장 석권 기대. 공매도 제도 폐지 요구. 주당 10만원 이상 정상 가격 제시. 반등 및 우상향 전망.</t>
+          <t>희토류 없는 백색 LED 개발 및 세계 1위 기업이라는 점을 강조하며 기술력에 대한 긍정적 평가.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '공매도']</t>
+          <t>['LED', '희토류', '기술력']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15810</v>
+        <v>15880</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.57%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>70178454790</v>
+        <v>79127787590</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3985</v>
+        <v>3980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.36%</t>
+          <t>'-1.49%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="H12" t="n">
         <v>1.43</v>
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>85837351162</v>
+        <v>86109169242</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61400</v>
+        <v>7320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.23%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>453</v>
+        <v>281</v>
       </c>
       <c r="H13" t="n">
-        <v>41.76</v>
+        <v>25.3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62800</v>
+        <v>7450</v>
       </c>
       <c r="K13" t="n">
-        <v>62300</v>
+        <v>7350</v>
       </c>
       <c r="L13" t="n">
-        <v>62800</v>
+        <v>7570</v>
       </c>
       <c r="M13" t="n">
-        <v>60400</v>
+        <v>7220</v>
       </c>
       <c r="N13" t="n">
-        <v>41.55</v>
+        <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>124127432900</v>
+        <v>16616562970</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>17950</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>7010</v>
       </c>
       <c r="R13" t="n">
-        <v>-65000</v>
+        <v>-46000</v>
       </c>
       <c r="S13" t="n">
-        <v>-81000</v>
+        <v>-8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7280</v>
+        <v>61700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.28%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
-        <v>279</v>
+        <v>470</v>
       </c>
       <c r="H14" t="n">
-        <v>25.3</v>
+        <v>41.76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7450</v>
+        <v>62800</v>
       </c>
       <c r="K14" t="n">
-        <v>7350</v>
+        <v>62300</v>
       </c>
       <c r="L14" t="n">
-        <v>7570</v>
+        <v>62800</v>
       </c>
       <c r="M14" t="n">
-        <v>7220</v>
+        <v>60400</v>
       </c>
       <c r="N14" t="n">
-        <v>25.32</v>
+        <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>14880229690</v>
+        <v>134970097300</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>7010</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>-46000</v>
+        <v>-65000</v>
       </c>
       <c r="S14" t="n">
-        <v>-8000</v>
+        <v>-81000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,222 +1752,222 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>225000</v>
+        <v>8350</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>116</v>
       </c>
       <c r="F15" t="n">
-        <v>455</v>
+        <v>67</v>
       </c>
       <c r="G15" t="n">
-        <v>1119</v>
+        <v>322</v>
       </c>
       <c r="H15" t="n">
-        <v>46.17</v>
+        <v>2.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>232000</v>
+        <v>8580</v>
       </c>
       <c r="K15" t="n">
-        <v>223500</v>
+        <v>11090</v>
       </c>
       <c r="L15" t="n">
-        <v>229500</v>
+        <v>11150</v>
       </c>
       <c r="M15" t="n">
-        <v>216500</v>
+        <v>8000</v>
       </c>
       <c r="N15" t="n">
-        <v>46.19</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>3686026755250</v>
+        <v>31420006515</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>19270</v>
       </c>
       <c r="Q15" t="n">
-        <v>94500</v>
+        <v>2135</v>
       </c>
       <c r="R15" t="n">
-        <v>538000</v>
+        <v>-396000</v>
       </c>
       <c r="S15" t="n">
-        <v>241000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급이 다수 관찰되며, 주가 하락에 대한 정치적 책임론이 제기됨.</t>
+          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정치', '주가 하락', '책임론']</t>
+          <t>['광반도체', '와이캅3', '환기']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6410</v>
+        <v>225000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>449</v>
       </c>
       <c r="G16" t="n">
-        <v>92</v>
+        <v>1125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.85</v>
+        <v>46.17</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6640</v>
+        <v>232000</v>
       </c>
       <c r="K16" t="n">
-        <v>7210</v>
+        <v>223500</v>
       </c>
       <c r="L16" t="n">
-        <v>7500</v>
+        <v>229500</v>
       </c>
       <c r="M16" t="n">
-        <v>6230</v>
+        <v>216500</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9</v>
+        <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>32736615240</v>
+        <v>4229956155250</v>
       </c>
       <c r="P16" t="n">
-        <v>9820</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>4000</v>
+        <v>94500</v>
       </c>
       <c r="R16" t="n">
-        <v>-27000</v>
+        <v>538000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>241000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
+          <t>정권 교체 요구와 함께 삼성전자 주가 부양에 대한 기대가 혼재. 정치적 발언이 다수.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공급 계약', '유통 물량', '주포']</t>
+          <t>['정치', '주가', '주주환원']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8270</v>
+        <v>6430</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.16%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>322</v>
+        <v>93</v>
       </c>
       <c r="H17" t="n">
-        <v>2.67</v>
+        <v>0.85</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8580</v>
+        <v>6640</v>
       </c>
       <c r="K17" t="n">
-        <v>11090</v>
+        <v>7210</v>
       </c>
       <c r="L17" t="n">
-        <v>11150</v>
+        <v>7500</v>
       </c>
       <c r="M17" t="n">
-        <v>8000</v>
+        <v>6230</v>
       </c>
       <c r="N17" t="n">
-        <v>2.66</v>
+        <v>0.9</v>
       </c>
       <c r="O17" t="n">
-        <v>31337216265</v>
+        <v>32799744980</v>
       </c>
       <c r="P17" t="n">
-        <v>19270</v>
+        <v>9820</v>
       </c>
       <c r="Q17" t="n">
-        <v>2135</v>
+        <v>4000</v>
       </c>
       <c r="R17" t="n">
-        <v>-396000</v>
+        <v>-27000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>서울바이오시스의 독점 기술 및 신규 기술(광통신, 와이캅3)에 대한 기대감 존재. 환기 문제 해소 및 외인 유입 가능성 언급.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광반도체', '와이캅3', '환기']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54500</v>
+        <v>54800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.88%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.2</v>
       </c>
       <c r="E18" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F18" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G18" t="n">
-        <v>1387</v>
+        <v>1417</v>
       </c>
       <c r="H18" t="n">
         <v>22.14</v>
@@ -2082,7 +2082,7 @@
         <v>22.34</v>
       </c>
       <c r="O18" t="n">
-        <v>119983956150</v>
+        <v>134197486950</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 관련 긍정적 뉴스가 있으나, 체코 원전 사업 관련 부정적 언급과 함께 정부 정책에 대한 불만 표현이 혼재됨.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 관련 긍정적 뉴스에도 불구하고, 실적과 무관한 국장 흐름에 대한 비판.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SMR', '원전 수주', '실적']</t>
+          <t>['SMR', '원전', '수주']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22550</v>
+        <v>22600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-4.24%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.63</v>
       </c>
       <c r="E19" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F19" t="n">
         <v>180</v>
@@ -2174,7 +2174,7 @@
         <v>12.23</v>
       </c>
       <c r="O19" t="n">
-        <v>102463678475</v>
+        <v>107146579275</v>
       </c>
       <c r="P19" t="n">
         <v>59300</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>174000</v>
+        <v>174100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-5.38%</t>
+          <t>'-5.33%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2240,7 +2240,7 @@
         <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>766178676600</v>
+        <v>853077209600</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10900</v>
+        <v>10920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-6.20%</t>
+          <t>'-6.02%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F21" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G21" t="n">
-        <v>1560</v>
+        <v>1593</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2358,7 +2358,7 @@
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>70062112580</v>
+        <v>71993532980</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1411000</v>
+        <v>1418000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.54%</t>
+          <t>'-7.08%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G22" t="n">
-        <v>1189</v>
+        <v>1218</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>4413193597000</v>
+        <v>5098056401000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 주가 반등에 대한 기대감이 일부 존재하나, 감정적 표현과 불확실한 전망이 주를 이룸. 자사주 매입 관련 언급이 있으나 구체적인 근거 부족.</t>
+          <t>하락세 속에서 자사주 매입 호재와 AI 혁명 기대감이 공존. 정치적 언급 포함.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주 매입', '주가 반등', 'AI']</t>
+          <t>['자사주매입', 'AI', '실적']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2516,7 +2516,7 @@
         <v>72</v>
       </c>
       <c r="G23" t="n">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>52974447170</v>
+        <v>53398300370</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7010</v>
+        <v>7220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-11.27%</t>
+          <t>'-8.61%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>18569393555</v>
+        <v>18738471515</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>95800</v>
+        <v>95600</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-11.54%</t>
+          <t>'-11.73%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.03</v>
       </c>
       <c r="E25" t="n">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="F25" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G25" t="n">
-        <v>1574</v>
+        <v>1643</v>
       </c>
       <c r="H25" t="n">
         <v>39.05</v>
@@ -2726,7 +2726,7 @@
         <v>39.08</v>
       </c>
       <c r="O25" t="n">
-        <v>183141990500</v>
+        <v>208488992100</v>
       </c>
       <c r="P25" t="n">
         <v>212500</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>큰 폭의 주가 하락에 대한 불만이 표출되며, 회사 실적 및 주가 조작 의혹에 대한 부정적 인식이 강하게 나타남. 컨센서스 대비 호실적 언급도 있으나 하락세를 상쇄하지 못함.</t>
+          <t>급락세와 함께 주가 조작 의혹 및 실적 발표에 대한 불만이 제기됨. 정치적 언급도 다수.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['주가 하락', '실적', '주가 조작']</t>
+          <t>['급락', '실적', '주가조작']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2786,13 +2786,13 @@
         <v>-0.26</v>
       </c>
       <c r="E26" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F26" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G26" t="n">
-        <v>653</v>
+        <v>689</v>
       </c>
       <c r="H26" t="n">
         <v>14.2</v>
@@ -2818,7 +2818,7 @@
         <v>14.46</v>
       </c>
       <c r="O26" t="n">
-        <v>213193433750</v>
+        <v>216778896350</v>
       </c>
       <c r="P26" t="n">
         <v>198000</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>실적 발표 지연 및 주가 급락. SK하이닉스 물량 확대 관련 뉴스 언급 및 목표가 상향 분석.</t>
+          <t>실적 기대감에도 불구하고 큰 폭의 하락세를 보이며 투자자들의 혼란 가중. 목표가 상향 증권사 리포트 존재.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['실적', 'SK하이닉스', '목표가']</t>
+          <t>['실적', '목표가 상향', '주가 하락']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2867,24 +2867,24 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13680</v>
+        <v>13760</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>'-19.53%</t>
+          <t>'-19.06%</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F27" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G27" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H27" t="n">
         <v>0.66</v>
@@ -2910,7 +2910,7 @@
         <v>0.65</v>
       </c>
       <c r="O27" t="n">
-        <v>72871334870</v>
+        <v>73075216790</v>
       </c>
       <c r="P27" t="n">
         <v>28800</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회와 반도체 시장 약세 속에서 주가 하락에 대한 불만이 제기됨. 일부는 매수 기회로 보지만, 전체적으로 부정적인 논조가 강함.</t>
+          <t>보호예수 물량 출회 및 시장 상황에 대한 부정적 의견. 일부 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '주가 하락']</t>
+          <t>['보호예수', '반도체', '매수']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2970,13 +2970,13 @@
         <v>1.45</v>
       </c>
       <c r="E28" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F28" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G28" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H28" t="n">
         <v>4.8</v>
@@ -3002,7 +3002,7 @@
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>8537172363</v>
+        <v>8552014878</v>
       </c>
       <c r="P28" t="n">
         <v>5700</v>
@@ -3018,16 +3018,16 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>하한가 기록 및 부도, 상폐 우려가 제기되며 매우 부정적인 심리가 지배적임. 납입 여부 및 공시 내용에 대한 불확실성이 높으며, 주가 조작 가능성에 대한 의혹도 제기됨.</t>
+          <t>하한가 및 상폐 우려와 함께 자금 납입 관련 불확실성 제기. 공시 시점에 대한 언급.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['하한가', '부도', '상폐']</t>
+          <t>['하한가', '상폐', '자금납입']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3051,24 +3051,24 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9410</v>
+        <v>9360</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>'-37.27%</t>
+          <t>'-37.60%</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="F29" t="n">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="G29" t="n">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="H29" t="n">
         <v>3.05</v>
@@ -3088,19 +3088,19 @@
         <v>12700</v>
       </c>
       <c r="M29" t="n">
-        <v>9380</v>
+        <v>9360</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>155476940960</v>
+        <v>155921868560</v>
       </c>
       <c r="P29" t="n">
         <v>12700</v>
       </c>
       <c r="Q29" t="n">
-        <v>9380</v>
+        <v>9360</v>
       </c>
       <c r="R29" t="n">
         <v>-41000</v>
@@ -3110,16 +3110,16 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>높은 영업이익과 매출액을 근거로 긍정적 전망이 제시되며, 경쟁사(인텔리빅스) 대비 우수한 재무 상태를 강조함. 상장 초기의 변동성에 대한 언급도 있음.</t>
+          <t>인텔리빅스와 비교하며 높은 영업이익을 근거로 상승 기대감 표출. 실내 골프 관련 내용 언급.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>['영업이익', '매출', '알짜배기']</t>
+          <t>['영업이익', '상승', '실내골프']</t>
         </is>
       </c>
       <c r="X29" t="n">

--- a/data/trending_integrated_20261030_15.xlsx
+++ b/data/trending_integrated_20261030_15.xlsx
@@ -581,10 +581,10 @@
         <v>800</v>
       </c>
       <c r="F2" t="n">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="G2" t="n">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1189537526740</v>
+        <v>1190039540740</v>
       </c>
       <c r="P2" t="n">
         <v>35350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>AI 관련주로 분류되며 강한 상승 기대감 표출. IPO 관련 내용 언급.</t>
+          <t>AI 테마 상승 기대감 속 급등하는 주가. 정부 지원 AI 회사 언급하며 긍정적인 전망 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['AI', 'IPO', '상승']</t>
+          <t>['AI 테마', '신규주', '정부 지원']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3000</v>
+        <v>3185</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.45%</t>
+          <t>'+30.00%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
         <v>0.79</v>
@@ -693,7 +693,7 @@
         <v>2460</v>
       </c>
       <c r="L3" t="n">
-        <v>3110</v>
+        <v>3185</v>
       </c>
       <c r="M3" t="n">
         <v>2335</v>
@@ -702,10 +702,10 @@
         <v>0.63</v>
       </c>
       <c r="O3" t="n">
-        <v>13786409271</v>
+        <v>14587866746</v>
       </c>
       <c r="P3" t="n">
-        <v>3170</v>
+        <v>3185</v>
       </c>
       <c r="Q3" t="n">
         <v>880</v>
@@ -762,13 +762,13 @@
         <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F4" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G4" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -794,7 +794,7 @@
         <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>145543239510</v>
+        <v>145557827010</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -860,7 +860,7 @@
         <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H5" t="n">
         <v>13.29</v>
@@ -886,7 +886,7 @@
         <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>11654105465</v>
+        <v>11656605305</v>
       </c>
       <c r="P5" t="n">
         <v>13670</v>
@@ -952,7 +952,7 @@
         <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>42732270650</v>
+        <v>42742251950</v>
       </c>
       <c r="P6" t="n">
         <v>16620</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>급등 및 하락에 대한 혼조된 의견. 건설주로서의 역할에 대한 언급.</t>
+          <t>건설주 상승 기대감 속 연상 행진. 유증 실패 및 쌍봉 출현 등 주의 의견도 공존.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['급등', '건설', '주가']</t>
+          <t>['건설주', '연상', '유증 실패']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.36</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
         <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="H7" t="n">
         <v>4.69</v>
@@ -1070,7 +1070,7 @@
         <v>5.05</v>
       </c>
       <c r="O7" t="n">
-        <v>137567866750</v>
+        <v>137606275750</v>
       </c>
       <c r="P7" t="n">
         <v>50600</v>
@@ -1130,13 +1130,13 @@
         <v>-0.9</v>
       </c>
       <c r="E8" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="H8" t="n">
         <v>7.15</v>
@@ -1162,7 +1162,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>61422048125</v>
+        <v>61426190285</v>
       </c>
       <c r="P8" t="n">
         <v>49800</v>
@@ -1222,13 +1222,13 @@
         <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H9" t="n">
         <v>23.82</v>
@@ -1254,7 +1254,7 @@
         <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>77582928100</v>
+        <v>77583954100</v>
       </c>
       <c r="P9" t="n">
         <v>97900</v>
@@ -1314,13 +1314,13 @@
         <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F10" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G10" t="n">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="H10" t="n">
         <v>15.04</v>
@@ -1346,7 +1346,7 @@
         <v>15.08</v>
       </c>
       <c r="O10" t="n">
-        <v>66303063595</v>
+        <v>66304134475</v>
       </c>
       <c r="P10" t="n">
         <v>18960</v>
@@ -1406,13 +1406,13 @@
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="n">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H11" t="n">
         <v>28.13</v>
@@ -1438,7 +1438,7 @@
         <v>28.07</v>
       </c>
       <c r="O11" t="n">
-        <v>79127787590</v>
+        <v>79128772150</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 실적 호조 및 미국 조선주 강세와 대비되는 국내 조선주 약세. 델핀 FLNG 2호기 수주 기대감.</t>
+          <t>실적 서프라이즈 기대감과 미국 조선주 강세 속 국내 조선주 약세에 대한 의문 제기. 수주 가능성 뉴스 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', '수주', '조선주']</t>
+          <t>['실적 서프라이즈', '수주 가능성', '조선주 약세']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1530,7 +1530,7 @@
         <v>2.2</v>
       </c>
       <c r="O12" t="n">
-        <v>86109169242</v>
+        <v>86123747982</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1590,13 +1590,13 @@
         <v>-0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F13" t="n">
         <v>36</v>
       </c>
       <c r="G13" t="n">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H13" t="n">
         <v>25.3</v>
@@ -1622,7 +1622,7 @@
         <v>25.32</v>
       </c>
       <c r="O13" t="n">
-        <v>16616562970</v>
+        <v>16618305130</v>
       </c>
       <c r="P13" t="n">
         <v>17950</v>
@@ -1682,13 +1682,13 @@
         <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="H14" t="n">
         <v>41.76</v>
@@ -1714,7 +1714,7 @@
         <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>134970097300</v>
+        <v>135143350900</v>
       </c>
       <c r="P14" t="n">
         <v>67300</v>
@@ -1780,7 +1780,7 @@
         <v>67</v>
       </c>
       <c r="G15" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="H15" t="n">
         <v>2.67</v>
@@ -1806,7 +1806,7 @@
         <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>31420006515</v>
+        <v>31426068615</v>
       </c>
       <c r="P15" t="n">
         <v>19270</v>
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="G16" t="n">
-        <v>1125</v>
+        <v>1154</v>
       </c>
       <c r="H16" t="n">
         <v>46.17</v>
@@ -1898,7 +1898,7 @@
         <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>4229956155250</v>
+        <v>4230108030250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>정권 교체 요구와 함께 삼성전자 주가 부양에 대한 기대가 혼재. 정치적 발언이 다수.</t>
+          <t>정치적 불만 표출 속 주가 하락 방어 시도. 정부 정책 비판과 함께 주가 부양에 대한 기대감 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['정치', '주가', '주주환원']</t>
+          <t>['정부 정책', '주가 부양', '시장 방어']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H17" t="n">
         <v>0.85</v>
@@ -1990,7 +1990,7 @@
         <v>0.9</v>
       </c>
       <c r="O17" t="n">
-        <v>32799744980</v>
+        <v>32801146720</v>
       </c>
       <c r="P17" t="n">
         <v>9820</v>
@@ -2050,13 +2050,13 @@
         <v>-0.2</v>
       </c>
       <c r="E18" t="n">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F18" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G18" t="n">
-        <v>1417</v>
+        <v>1422</v>
       </c>
       <c r="H18" t="n">
         <v>22.14</v>
@@ -2082,7 +2082,7 @@
         <v>22.34</v>
       </c>
       <c r="O18" t="n">
-        <v>134197486950</v>
+        <v>134211789750</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2142,13 +2142,13 @@
         <v>-0.63</v>
       </c>
       <c r="E19" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F19" t="n">
         <v>180</v>
       </c>
       <c r="G19" t="n">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="H19" t="n">
         <v>11.6</v>
@@ -2174,7 +2174,7 @@
         <v>12.23</v>
       </c>
       <c r="O19" t="n">
-        <v>107146579275</v>
+        <v>107173925275</v>
       </c>
       <c r="P19" t="n">
         <v>59300</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>RE100 1조원 승인 및 미국 카터스빌 모듈 완판 소식에도 불구하고 주가 하락 및 유증에 대한 불만, 의도적 주가 누르기 의혹 제기.</t>
+          <t>실적 턴어라운드에도 불구하고 급락하는 주가에 대한 불만 표출. 유상증자, 주가 누르기 의혹 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['RE100', '카터스빌', '유증']</t>
+          <t>['실적 턴어라운드', '주가 누르기', '유상증자']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.13</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F20" t="n">
         <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H20" t="n">
         <v>74.87</v>
@@ -2266,7 +2266,7 @@
         <v>75</v>
       </c>
       <c r="O20" t="n">
-        <v>853077209600</v>
+        <v>853378576700</v>
       </c>
       <c r="P20" t="n">
         <v>243500</v>
@@ -2326,13 +2326,13 @@
         <v>0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="F21" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G21" t="n">
-        <v>1593</v>
+        <v>1611</v>
       </c>
       <c r="H21" t="n">
         <v>9.73</v>
@@ -2358,7 +2358,7 @@
         <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>71993532980</v>
+        <v>72013691300</v>
       </c>
       <c r="P21" t="n">
         <v>40350</v>
@@ -2370,7 +2370,7 @@
         <v>-504000</v>
       </c>
       <c r="S21" t="n">
-        <v>-81000</v>
+        <v>27000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         <v>800</v>
       </c>
       <c r="F22" t="n">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="G22" t="n">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="H22" t="n">
         <v>48.72</v>
@@ -2450,7 +2450,7 @@
         <v>48.66</v>
       </c>
       <c r="O22" t="n">
-        <v>5098056401000</v>
+        <v>5098623601000</v>
       </c>
       <c r="P22" t="n">
         <v>2987000</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>하락세 속에서 자사주 매입 호재와 AI 혁명 기대감이 공존. 정치적 언급 포함.</t>
+          <t>정부 정책 비판과 함께 주가 조작 의혹 제기. AI 관련 기업 주가 폭락 속 개인 투자자들의 분노 표출.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주매입', 'AI', '실적']</t>
+          <t>['AI 혁명', '주가 조작', '정부 정책']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2513,10 +2513,10 @@
         <v>135</v>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G23" t="n">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="H23" t="n">
         <v>3.13</v>
@@ -2542,7 +2542,7 @@
         <v>3.33</v>
       </c>
       <c r="O23" t="n">
-        <v>53398300370</v>
+        <v>53415702170</v>
       </c>
       <c r="P23" t="n">
         <v>31500</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>27년까지의 성장 전망 및 광통신 섹터 호재에도 불구하고 국내 증시 불신으로 인한 주가 하락, 공매도 세력 비판.</t>
+          <t>국내 증시 불신 속 광통신주 약세. 호재에도 불구하고 주가 하락에 대한 불만 토로.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['광통신', '특허', '호재']</t>
+          <t>['광통신주', '국내 증시 불신', '호재']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2602,13 +2602,13 @@
         <v>-0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="H24" t="n">
         <v>0.39</v>
@@ -2634,7 +2634,7 @@
         <v>0.42</v>
       </c>
       <c r="O24" t="n">
-        <v>18738471515</v>
+        <v>18764059195</v>
       </c>
       <c r="P24" t="n">
         <v>10300</v>
@@ -2694,13 +2694,13 @@
         <v>-0.03</v>
       </c>
       <c r="E25" t="n">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="F25" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G25" t="n">
-        <v>1643</v>
+        <v>1697</v>
       </c>
       <c r="H25" t="n">
         <v>39.05</v>
@@ -2726,7 +2726,7 @@
         <v>39.08</v>
       </c>
       <c r="O25" t="n">
-        <v>208488992100</v>
+        <v>208490330500</v>
       </c>
       <c r="P25" t="n">
         <v>212500</v>
@@ -2786,13 +2786,13 @@
         <v>-0.26</v>
       </c>
       <c r="E26" t="n">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="F26" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G26" t="n">
-        <v>689</v>
+        <v>799</v>
       </c>
       <c r="H26" t="n">
         <v>14.2</v>
@@ -2818,7 +2818,7 @@
         <v>14.46</v>
       </c>
       <c r="O26" t="n">
-        <v>216778896350</v>
+        <v>216853760150</v>
       </c>
       <c r="P26" t="n">
         <v>198000</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>실적 기대감에도 불구하고 큰 폭의 하락세를 보이며 투자자들의 혼란 가중. 목표가 상향 증권사 리포트 존재.</t>
+          <t>컨센서스 상회하는 호실적 발표와 함께 목표가 상향. 실적 기반 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['실적', '목표가 상향', '주가 하락']</t>
+          <t>['실적', '어닝 서프라이즈', '목표가 상향']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F27" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G27" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H27" t="n">
         <v>0.66</v>
@@ -2910,7 +2910,7 @@
         <v>0.65</v>
       </c>
       <c r="O27" t="n">
-        <v>73075216790</v>
+        <v>73097741910</v>
       </c>
       <c r="P27" t="n">
         <v>28800</v>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회 및 시장 상황에 대한 부정적 의견. 일부 매수 기회 언급.</t>
+          <t>보호예수 물량 출회와 급락하는 주가에 대한 불만. 시장 개판이라는 평가와 함께 투매 및 손실 경험 공유.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '매수']</t>
+          <t>['보호예수', '급락', '시장 개판']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2970,13 +2970,13 @@
         <v>1.45</v>
       </c>
       <c r="E28" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F28" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G28" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="H28" t="n">
         <v>4.8</v>
@@ -3002,7 +3002,7 @@
         <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>8552014878</v>
+        <v>8552085273</v>
       </c>
       <c r="P28" t="n">
         <v>5700</v>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>하한가 및 상폐 우려와 함께 자금 납입 관련 불확실성 제기. 공시 시점에 대한 언급.</t>
+          <t>연이은 하한가와 부도, 상폐 우려 속 투자자들의 공포 심리. 유증 납입 관련 불확실성 언급.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>['하한가', '상폐', '자금납입']</t>
+          <t>['하한가', '부도', '상폐 우려']</t>
         </is>
       </c>
       <c r="X28" t="n">
@@ -3062,13 +3062,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F29" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G29" t="n">
-        <v>1045</v>
+        <v>1061</v>
       </c>
       <c r="H29" t="n">
         <v>3.05</v>
@@ -3094,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>155921868560</v>
+        <v>155981594720</v>
       </c>
       <c r="P29" t="n">
         <v>12700</v>
